--- a/Codelist Excel Files and Conversion Templates to XML/sampleType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/sampleType.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Controlled vocabulary for diggs:SampleType/type, describing sample form only - the physical means by which a material sample was obtained (tube, drive, core, bulk, block, or fluid/gas extraction technique). Deliberately excludes sample class, sampler brand, insertion method, condition and purpose, each already modeled as its own diggs:Sample property (classification, samplerInsertionMethod, condition, purpose) or, for proprietary sampler brands, as an AlternateNames synonym on the relevant term here rather than a first-class code. Anchored on ISO 22475-1:2021 and the AGS4.2 SAMP_TYPE vocabulary rather than ASTM designations, since ASTM's sampling-practice family (D1587, D3550, D2113, D4220) has been withdrawn wholesale with no ASTM replacement named; an ASTM designation is cited as a secondary anchor only where one still stands. Not bound to diggs:TargetSampleType - that type deliberately has no type-equivalent property (see its own documentation in core/Core.xsd), so this vocabulary serves the as-built diggs:Sample object only.</t>
+          <t>Controlled vocabulary for diggs:SampleType/type, describing sample form only - the physical means by which a material sample was obtained (tube, drive, core, bulk, block, or fluid/gas extraction technique). Deliberately excludes sample class, sampler brand, insertion method, condition and purpose, each already modeled as its own diggs:Sample property (classification, samplerInsertionMethod, condition, purpose) or, for proprietary sampler brands, as an AlternateNames synonym on the relevant term here rather than a first-class code. Anchored on ISO 22475-1:2021 and the AGS4.2 SAMP_TYPE vocabulary rather than ASTM designations, since ASTM's sampling-practice family (D1587, D3550, D2113, D4220) has been withdrawn wholesale with no ASTM replacement named; an ASTM designation is cited as a secondary anchor only where one still stands. Not bound to diggs:DesignSampleType - that type deliberately has no type-equivalent property (see its own documentation in core/Core.xsd), so this vocabulary serves the as-built diggs:Sample object only.</t>
         </is>
       </c>
     </row>
